--- a/BASE DE DATOS.xlsx
+++ b/BASE DE DATOS.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\4_NX5a\09_Information\10_FTQ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\LAUNCH MANAGEMENT\1 KI\5_MB MMA\09_Information\10_FTQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35C4435-97D1-4CE5-BD79-745B6F832C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37415832-24D7-4459-BC2D-E251FB0DFDD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{439F1396-05A1-464E-A03B-8C77E5396FAA}"/>
   </bookViews>
   <sheets>
-    <sheet name="BASE DE DATOS RIVIAN" sheetId="1" r:id="rId1"/>
+    <sheet name="BASE DE DATOS" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS RIVIAN'!$B$4:$J$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS'!$B$4:$J$98</definedName>
     <definedName name="DATA_01">[1]Data_Lineal!$H$4:$Y$30</definedName>
     <definedName name="DB_01">#REF!</definedName>
     <definedName name="DB_CAP01">'[2]CAPACIDAD (1)'!$X$9:$AM$29</definedName>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="85">
   <si>
     <t>*</t>
   </si>
@@ -111,154 +111,214 @@
     <t>PRODUCCIÓN</t>
   </si>
   <si>
-    <t>1100A</t>
+    <t>SCR MMA</t>
   </si>
   <si>
-    <t>Falso rechazo Op.1100A</t>
+    <t>EOL</t>
   </si>
   <si>
-    <t>1100B</t>
+    <t>Mal enrollado de cables Op.200</t>
   </si>
   <si>
-    <t>Hyundai/KIA</t>
+    <t>Mal ensamble con cable AB dañado Op.150</t>
   </si>
   <si>
-    <t>Falta de puntos de grasa Op.100</t>
+    <t>Mala colocación de cable AB en doblez Op.150</t>
   </si>
   <si>
-    <t>Corredera mal posicionada Op.400</t>
+    <t>Cables dañados por doblez Op.150</t>
   </si>
   <si>
-    <t>Corto de soldadura Op.800</t>
+    <t>Falla en inspección visual no detecta piezas NOK Op.200</t>
   </si>
   <si>
-    <t>Falta de soldadura Op.800</t>
+    <t>Latch y Resorte no llegan a posición correcta Op.300</t>
   </si>
   <si>
-    <t>Falta de soldadura Op.1100A</t>
+    <t>Falla 3320.041 Op.EOL</t>
   </si>
   <si>
-    <t>Lever Barcode Scan Facture Op.300</t>
+    <t>Falla 3310.011 Op.EOL</t>
   </si>
   <si>
-    <t>Falla en lectura de Scanner Op.300</t>
+    <t>Falsos rechazos Op.EOL</t>
   </si>
   <si>
-    <t>Falla de inspección visual Op.200</t>
+    <t>Falla 3550.002 Op.EOL</t>
   </si>
   <si>
-    <t>Falla de inspección visual Op.300</t>
+    <t>Falla 6000.001 Op.EOL</t>
   </si>
   <si>
-    <t>Falla de inspección visual Op.600</t>
+    <t>Falla 2110.020 Op.EOL</t>
   </si>
   <si>
-    <t>Falla de inspección visual Op.400</t>
+    <t>Cable and Mark NG (Ventanita) Op.EOL</t>
   </si>
   <si>
-    <t>Falla en lectura de Scanner Op.400</t>
+    <t>SCCM MMA</t>
   </si>
   <si>
-    <t>Falla en atornillado Op.700</t>
+    <t>Falla de inspección visual en curvas sin NG Op.100</t>
   </si>
   <si>
-    <t>Falla sin especificación Op.900</t>
+    <t>Dispensado de Grasa No Uniforme en Engrane sin NG Op.200</t>
   </si>
   <si>
-    <t>Mal embobinado en spiral Op.1100A</t>
+    <t>Sensor no detecta mesa giratoria Op.400</t>
   </si>
   <si>
-    <t>Falla de sensor de slai Op.400</t>
+    <t>Falla en inspección visual de Ruteo de Arnes Op.700</t>
   </si>
   <si>
-    <t>Falla de sensor S$9 Op.400</t>
+    <t>Falla en alimentador de Tornillos Op.800</t>
   </si>
   <si>
-    <t>Material Towerdid Op.400</t>
+    <t>Falla de inspección visual en Mordaza Métalica sin NG Op.100</t>
   </si>
   <si>
-    <t xml:space="preserve">SFC 965827AGG00003 is not in queue at operation Op.400 </t>
+    <t>Falla de Etiqueta por Guarda sin NG Op.300</t>
   </si>
   <si>
-    <t>Sin especificar Op. 600</t>
+    <t>Inspección visual  no detecta PCB sin conector Op.600</t>
   </si>
   <si>
-    <t>Sin especificar ok Op. 600</t>
+    <t>Falla de inspección visual  Op.700</t>
   </si>
   <si>
-    <t>Falso Rechazo (version de SCR) Op.700</t>
+    <t>No pide Inspección visual  del SCAS Op.700</t>
   </si>
   <si>
-    <t>Falta de grasa en PCB Op.400</t>
+    <t>Mal enclipsado de Engrane en Housing (SAS) Op.200</t>
   </si>
   <si>
-    <t>Detecta piezas de sobre-producción Op.400</t>
+    <t>Falla de Robot de enclipsado de Engrane en Housing (SAS) Op.200</t>
   </si>
   <si>
-    <t>Mezcla de material con index incorrecto Op.700</t>
+    <t>Falla Mécanica en nido giratorio Op.500</t>
   </si>
   <si>
-    <t>Falla 0090.040 Op.1100A</t>
+    <t>Falla de inspección visual en Stator Housing Op.100</t>
   </si>
   <si>
-    <t>Falla  0040.074 Op.1100A</t>
+    <t>Falla de inspección visual en Rotor Housing Op.100</t>
   </si>
   <si>
-    <t>Falla 0400.020 Op.1100A</t>
+    <t>Falla de altura de cable AB Op.200</t>
   </si>
   <si>
-    <t>Falla 0400.030 Op.1100A</t>
+    <t>Cable Dummy dañado Op.200</t>
   </si>
   <si>
-    <t>Falla 0060.005 Op.1100A</t>
+    <t>Falla "Codigo de barra no corresponde a la versión"  sin NOK Op.300</t>
   </si>
   <si>
-    <t>Falla 0090.004 Op.1100B</t>
+    <t>Falla 3110.004 Op.EOL</t>
   </si>
   <si>
-    <t>Detecta pieza sin pasar en operación anterior Op.700</t>
+    <t>Falla 2270.004 Op.EOL</t>
   </si>
   <si>
-    <t>Safe Launch</t>
+    <t>Falla de inspección visual no permite colocar Bearing Ring Op.100</t>
   </si>
   <si>
-    <t>Falla de secuencia Op.100</t>
+    <t>Falla 2110.010 Op.EOL</t>
   </si>
   <si>
-    <t>Se pasa pieza de prueba (NOK) Op.200</t>
+    <t>Falla 2230.011 Op.EOL</t>
   </si>
   <si>
-    <t xml:space="preserve">Falla inspección visual por mal acomodo de Upper Housing Op.300 </t>
+    <t>Falla 3310.251 Op.EOL</t>
   </si>
   <si>
-    <t>Palanca dañada Op.300</t>
+    <t>Falla 3121.022 Op.EOL</t>
   </si>
   <si>
-    <t>Pide pieza master antes de fin de turno Op.400</t>
+    <t>Calibrador</t>
   </si>
   <si>
-    <t>MES - Falla de seguimiento en piezas Op.600</t>
+    <t>Mal ensamble por falla en detección de Elemento de compensación Op.400</t>
   </si>
   <si>
-    <t>Falla en scanner por lectura de etiqueta Op.200</t>
+    <t>Atorramiento de pieza en Nido Op.600</t>
   </si>
   <si>
-    <t>Falla en scanner por lectura de etiqueta Op.700</t>
+    <t>Falla de inspección visual en puntos de grasa Op.600</t>
   </si>
   <si>
-    <t>Picos en puntos de soldeo Op.800</t>
+    <t>Pruebas de Ruido</t>
   </si>
   <si>
-    <t>Falla en scanner por lectura de etiqueta Op.900</t>
+    <t>Calibrador de iluminación</t>
   </si>
   <si>
-    <t>Falla de secuencia Op.900</t>
+    <t>Falla por mal ensamble de SAS por gravedad sin NG Op.200</t>
   </si>
   <si>
-    <t>1000A</t>
+    <t>Se interrumpen cortinas de emergencia, detiene proceso Op.300</t>
   </si>
   <si>
-    <t>Falla 0200.010 Op.1100A</t>
+    <t>Banda transportadora no detecta piezas, se caen Op.600</t>
+  </si>
+  <si>
+    <t>Mal enclipsado de Spiral Op.700</t>
+  </si>
+  <si>
+    <t>Se interrumpen cortinas de emergencia, detiene proceso Op.800</t>
+  </si>
+  <si>
+    <t>Calibrador de Palancas</t>
+  </si>
+  <si>
+    <t>Falla por limites en Palancas Op.Calibrador de Palancas</t>
+  </si>
+  <si>
+    <t>Falla de sensor, no detecta pieza Op.Pruebas de Ruido</t>
+  </si>
+  <si>
+    <t>07/09/2026</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>12289507</t>
+  </si>
+  <si>
+    <t>Falla en proceso, no regresa Palanca a posición Op.Pruebas de Ruido</t>
+  </si>
+  <si>
+    <t>No inicia secuencia Op.Pruebas de Ruido</t>
+  </si>
+  <si>
+    <t>Calibrador de Iluminación</t>
+  </si>
+  <si>
+    <t>No inicia secuencia Op.Calibrador de Iluminación</t>
+  </si>
+  <si>
+    <t>Calibrador SAS1</t>
+  </si>
+  <si>
+    <t>Calibrador SAS2</t>
+  </si>
+  <si>
+    <t>Falla 9220.120 Op.Calibrador SAS1</t>
+  </si>
+  <si>
+    <t>Falla 4000.130 Op.Calibrador SAS2</t>
+  </si>
+  <si>
+    <t>Falla de inspección visual en resortes sin NG Op.100</t>
+  </si>
+  <si>
+    <t>Mala colocación del engrane grande Op.200</t>
+  </si>
+  <si>
+    <t>Mal ensamble de elemento de compensación en rodamiento Op.400</t>
+  </si>
+  <si>
+    <t>No ensambla tornillo</t>
   </si>
 </sst>
 </file>
@@ -340,7 +400,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -372,6 +432,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -381,7 +447,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="21">
     <dxf>
@@ -24363,7 +24429,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K82" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{421FD8D0-4DB9-4A88-8653-0AE7AE89107A}" name="Tabla158" displayName="Tabla158" ref="B4:K98" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CDAA4D20-2955-41E2-BD7E-9330E166FFF4}" name="Fecha" dataDxfId="18"/>
     <tableColumn id="9" xr3:uid="{F70BB124-92DE-4024-874C-EE3BA966CDE6}" name="Semana" dataDxfId="17">
@@ -24389,15 +24455,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S83" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{83880157-341F-4984-9DA8-9308A0C526D5}" name="Tabla2610" displayName="Tabla2610" ref="M4:S95" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{D688BA2E-A64E-4433-85E0-7EDBF854AF60}" name="Fecha" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{D3EA5E8D-DD68-48AC-8DAC-4A4077839479}" name="Semana" dataDxfId="5">
-      <calculatedColumnFormula>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{D688BA2E-A64E-4433-85E0-7EDBF854AF60}" name="07/09/2026" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{D3EA5E8D-DD68-48AC-8DAC-4A4077839479}" name="37" dataDxfId="5">
+      <calculatedColumnFormula>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2BBDA3EE-1089-4999-82D7-821DAA1CF033}" name="Línea" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{A327B0AF-C947-4083-8F0A-4A5908FD3558}" name="Maquina" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{58C9F38E-D89E-450A-9CAA-EFCECBECC74C}" name="Version" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{2BBDA3EE-1089-4999-82D7-821DAA1CF033}" name="SCCM MMA" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{A327B0AF-C947-4083-8F0A-4A5908FD3558}" name="Pruebas de Ruido" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{58C9F38E-D89E-450A-9CAA-EFCECBECC74C}" name="12289507" dataDxfId="2"/>
     <tableColumn id="5" xr3:uid="{5C95C72F-200A-46B3-A6FC-20E7D88A7BCD}" name="Defecto" dataDxfId="1"/>
     <tableColumn id="6" xr3:uid="{33109690-8A43-4F38-8F52-FD73CBA9F32F}" name="Cantidad" dataDxfId="0"/>
   </tableColumns>
@@ -24668,69 +24734,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A1B645-8848-474A-88BA-FA9209B01B4F}">
-  <dimension ref="A1:V830"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:V824"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
     <col min="2" max="2" width="13.21875" style="1" customWidth="1"/>
     <col min="3" max="4" width="11.5546875" style="1"/>
-    <col min="5" max="5" width="14.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.21875" style="1" customWidth="1"/>
     <col min="6" max="7" width="11.5546875" style="1"/>
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="0" style="2" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" style="2" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="11.5546875" style="2"/>
     <col min="12" max="12" width="2.44140625" customWidth="1"/>
     <col min="13" max="13" width="13.88671875" style="1" customWidth="1"/>
     <col min="14" max="14" width="10.5546875" style="1" customWidth="1"/>
     <col min="15" max="15" width="12.44140625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23" style="1" customWidth="1"/>
     <col min="17" max="17" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="57.109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="70.21875" style="1" customWidth="1"/>
     <col min="19" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
       <c r="K1" s="6"/>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
     </row>
     <row r="2" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
       <c r="K2" s="6"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.3">
       <c r="G3" s="1">
@@ -24771,20 +24838,20 @@
       <c r="K4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>7</v>
+      <c r="M4" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>3</v>
+        <v>60</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>72</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>2</v>
@@ -24795,115 +24862,115 @@
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B5" s="4">
-        <v>46217</v>
+        <v>46224</v>
       </c>
       <c r="C5" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E5" s="1">
         <v>100</v>
       </c>
       <c r="F5" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G5" s="1">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="H5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>9.6153846153846159E-3</v>
+        <v>0</v>
       </c>
       <c r="J5" s="1">
-        <f t="shared" ref="J5:J13" si="0">ABS(G$3-I5)</f>
-        <v>0.99038461538461542</v>
+        <f t="shared" ref="J5:J9" si="0">ABS(G$3-I5)</f>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.99038461538461542</v>
+        <v>1</v>
       </c>
       <c r="M5" s="4">
-        <v>46217</v>
+        <v>46224</v>
       </c>
       <c r="N5" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>30</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P5" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q5" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="S5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B6" s="4">
-        <v>46217</v>
+        <v>46224</v>
       </c>
       <c r="C6" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F6" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G6" s="1">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c r="H6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>9.433962264150943E-3</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1">
         <f t="shared" si="0"/>
-        <v>0.99056603773584906</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.99056603773584906</v>
+        <v>1</v>
       </c>
       <c r="M6" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N6" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>30</v>
       </c>
       <c r="O6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P6" s="1">
+        <v>150</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="P6" s="1">
-        <v>200</v>
-      </c>
-      <c r="Q6" s="9">
-        <v>12264732</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="S6" s="1">
         <v>1</v>
@@ -24911,344 +24978,344 @@
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
-        <v>46217</v>
+        <v>46224</v>
       </c>
       <c r="C7" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F7" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G7" s="1">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="H7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>2.6785714285714284E-2</v>
+        <v>0.11764705882352941</v>
       </c>
       <c r="J7" s="1">
         <f t="shared" si="0"/>
-        <v>0.9732142857142857</v>
+        <v>0.88235294117647056</v>
       </c>
       <c r="K7" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.9732142857142857</v>
+        <v>0.88235294117647056</v>
       </c>
       <c r="M7" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N7" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>30</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P7" s="1">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="Q7" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="S7" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
-        <v>46217</v>
+        <v>46224</v>
       </c>
       <c r="C8" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E8" s="1">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F8" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G8" s="1">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="H8" s="1">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.84042553191489366</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1">
         <f t="shared" si="0"/>
-        <v>0.15957446808510634</v>
+        <v>1</v>
       </c>
       <c r="K8" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.15957446808510634</v>
+        <v>1</v>
       </c>
       <c r="M8" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N8" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>30</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P8" s="1">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="Q8" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="S8" s="1">
-        <v>79</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="C9" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F9" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G9" s="1">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="H9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>1.0309278350515464E-2</v>
+        <v>0</v>
       </c>
       <c r="J9" s="1">
         <f t="shared" si="0"/>
-        <v>0.98969072164948457</v>
+        <v>1</v>
       </c>
       <c r="K9" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.98969072164948457</v>
+        <v>1</v>
       </c>
       <c r="M9" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N9" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>30</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P9" s="1">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="Q9" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="S9" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="C10" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="F10" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G10" s="1">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I10" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.12676056338028169</v>
       </c>
       <c r="J10" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" ref="J10:J12" si="1">ABS(G$3-I10)</f>
+        <v>0.87323943661971826</v>
       </c>
       <c r="K10" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.87323943661971826</v>
       </c>
       <c r="M10" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N10" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>30</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P10" s="1">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="Q10" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="S10" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="C11" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E11" s="1">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="F11" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G11" s="1">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="H11" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I11" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.12244897959183673</v>
+        <v>5.9701492537313432E-2</v>
       </c>
       <c r="J11" s="1">
-        <f t="shared" si="0"/>
-        <v>0.87755102040816324</v>
+        <f t="shared" si="1"/>
+        <v>0.94029850746268662</v>
       </c>
       <c r="K11" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.87755102040816324</v>
+        <v>0.94029850746268662</v>
       </c>
       <c r="M11" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N11" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>30</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P11" s="1">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="Q11" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>22</v>
       </c>
       <c r="S11" s="1">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="C12" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E12" s="1">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="F12" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G12" s="1">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I12" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.78260869565217395</v>
       </c>
       <c r="J12" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.21739130434782605</v>
       </c>
       <c r="K12" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.21739130434782605</v>
       </c>
       <c r="M12" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N12" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>30</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q12" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>23</v>
@@ -25259,57 +25326,57 @@
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="C13" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="G13" s="1">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="H13" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I13" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>3.896103896103896E-2</v>
+        <v>0.2391304347826087</v>
       </c>
       <c r="J13" s="1">
-        <f t="shared" si="0"/>
-        <v>0.96103896103896103</v>
+        <f>ABS(G$3-I13)</f>
+        <v>0.76086956521739135</v>
       </c>
       <c r="K13" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.96103896103896103</v>
+        <v>0.76086956521739135</v>
       </c>
       <c r="M13" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N13" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>30</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q13" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="S13" s="1">
         <v>1</v>
@@ -25317,23 +25384,23 @@
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B14" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="C14" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E14" s="1">
         <v>100</v>
       </c>
       <c r="F14" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G14" s="1">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="H14" s="1">
         <v>0</v>
@@ -25343,7 +25410,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <f t="shared" ref="J14:J22" si="1">ABS(G$3-I14)</f>
+        <f t="shared" ref="J14:J24" si="2">ABS(G$3-I14)</f>
         <v>1</v>
       </c>
       <c r="K14" s="5">
@@ -25351,511 +25418,511 @@
         <v>1</v>
       </c>
       <c r="M14" s="4">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="N14" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>30</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q14" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="S14" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="C15" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E15" s="1">
         <v>200</v>
       </c>
       <c r="F15" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G15" s="1">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="H15" s="1">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I15" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>4.9180327868852458E-2</v>
+        <v>0.4</v>
       </c>
       <c r="J15" s="1">
-        <f t="shared" si="1"/>
-        <v>0.95081967213114749</v>
+        <f t="shared" si="2"/>
+        <v>0.6</v>
       </c>
       <c r="K15" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.95081967213114749</v>
+        <v>0.6</v>
       </c>
       <c r="M15" s="4">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="N15" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>30</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P15" s="1">
-        <v>200</v>
+        <v>15</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q15" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="S15" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B16" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="C16" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E16" s="1">
         <v>300</v>
       </c>
       <c r="F16" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G16" s="1">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="H16" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I16" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="J16" s="1">
-        <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="K16" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
       <c r="M16" s="4">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="N16" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>30</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P16" s="1">
-        <v>300</v>
+        <v>15</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q16" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="S16" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B17" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="C17" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E17" s="1">
         <v>400</v>
       </c>
       <c r="F17" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G17" s="1">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="H17" s="1">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I17" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.45454545454545453</v>
+        <v>0</v>
       </c>
       <c r="J17" s="1">
-        <f t="shared" si="1"/>
-        <v>0.54545454545454541</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="K17" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.54545454545454541</v>
+        <v>1</v>
       </c>
       <c r="M17" s="4">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="N17" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>30</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P17" s="1">
-        <v>300</v>
+        <v>15</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q17" s="9">
-        <v>12264732</v>
+        <v>10532587</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S17" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B18" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="C18" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E18" s="1">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F18" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G18" s="1">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="H18" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.1038961038961039</v>
+        <v>0</v>
       </c>
       <c r="J18" s="1">
-        <f t="shared" si="1"/>
-        <v>0.89610389610389607</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="K18" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.89610389610389607</v>
+        <v>1</v>
       </c>
       <c r="M18" s="4">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="N18" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>30</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q18" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P18" s="1">
-        <v>300</v>
-      </c>
-      <c r="Q18" s="9">
-        <v>12264732</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="S18" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="C19" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E19" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F19" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G19" s="1">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="H19" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I19" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>8.1967213114754092E-2</v>
+        <v>0</v>
       </c>
       <c r="J19" s="1">
-        <f t="shared" si="1"/>
-        <v>0.91803278688524592</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="K19" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.91803278688524592</v>
+        <v>1</v>
       </c>
       <c r="M19" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="N19" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P19" s="1">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="Q19" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="S19" s="1">
-        <v>3</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="C20" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E20" s="1">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="F20" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G20" s="1">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="H20" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>5.4545454545454543E-2</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="J20" s="1">
-        <f t="shared" si="1"/>
-        <v>0.94545454545454544</v>
+        <f t="shared" si="2"/>
+        <v>0.77777777777777779</v>
       </c>
       <c r="K20" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.94545454545454544</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="M20" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="N20" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P20" s="1">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="Q20" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="S20" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B21" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="C21" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E21" s="1">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="F21" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G21" s="1">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="H21" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>7.2727272727272724E-2</v>
+        <v>0</v>
       </c>
       <c r="J21" s="1">
-        <f t="shared" si="1"/>
-        <v>0.92727272727272725</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="K21" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.92727272727272725</v>
+        <v>1</v>
       </c>
       <c r="M21" s="4">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="N21" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P21" s="1">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="Q21" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="S21" s="1">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B22" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="C22" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="E22" s="1">
+        <v>300</v>
       </c>
       <c r="F22" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G22" s="1">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H22" s="1">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I22" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>2.7777777777777776E-2</v>
+        <v>0.28260869565217389</v>
       </c>
       <c r="J22" s="1">
-        <f t="shared" si="1"/>
-        <v>0.97222222222222221</v>
+        <f t="shared" si="2"/>
+        <v>0.71739130434782616</v>
       </c>
       <c r="K22" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.97222222222222221</v>
+        <v>0.71739130434782616</v>
       </c>
       <c r="M22" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="N22" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P22" s="1">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="Q22" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="S22" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B23" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="C23" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
+      </c>
+      <c r="E23" s="1">
+        <v>400</v>
       </c>
       <c r="F23" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="G23" s="1">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
@@ -25865,7 +25932,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <f>ABS(G$3-I23)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K23" s="5">
@@ -25873,47 +25940,47 @@
         <v>1</v>
       </c>
       <c r="M23" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="N23" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P23" s="1">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="Q23" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="S23" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B24" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="C24" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E24" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F24" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="G24" s="1">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
@@ -25923,7 +25990,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <f t="shared" ref="J24:J32" si="2">ABS(G$3-I24)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K24" s="5">
@@ -25931,47 +25998,47 @@
         <v>1</v>
       </c>
       <c r="M24" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="N24" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P24" s="1">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="Q24" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="S24" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B25" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="C25" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E25" s="1">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="F25" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="G25" s="1">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -25981,7 +26048,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="J25:J32" si="3">ABS(G$3-I25)</f>
         <v>1</v>
       </c>
       <c r="K25" s="5">
@@ -25989,221 +26056,221 @@
         <v>1</v>
       </c>
       <c r="M25" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="N25" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P25" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="Q25" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="S25" s="1">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="C26" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E26" s="1">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="F26" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="G26" s="1">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I26" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="J26" s="1">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0.22222222222222221</v>
       </c>
       <c r="K26" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="M26" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="N26" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P26" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="Q26" s="9">
-        <v>12264732</v>
+        <v>12289497</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S26" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B27" s="4">
-        <v>46220</v>
+        <v>46231</v>
       </c>
       <c r="C27" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E27" s="1">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="F27" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="G27" s="1">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H27" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="J27" s="1">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0.93333333333333335</v>
       </c>
       <c r="K27" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="M27" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="N27" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P27" s="1">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="Q27" s="9">
-        <v>12264732</v>
+        <v>12289475</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>31</v>
       </c>
       <c r="S27" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B28" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="C28" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E28" s="1">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F28" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G28" s="1">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="H28" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I28" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>6.6666666666666666E-2</v>
+        <v>7.9207920792079209E-2</v>
       </c>
       <c r="J28" s="1">
-        <f t="shared" si="2"/>
-        <v>0.93333333333333335</v>
+        <f t="shared" si="3"/>
+        <v>0.92079207920792083</v>
       </c>
       <c r="K28" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.93333333333333335</v>
+        <v>0.92079207920792083</v>
       </c>
       <c r="M28" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="N28" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P28" s="1">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="Q28" s="9">
-        <v>12264732</v>
+        <v>12289475</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="S28" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B29" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="C29" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E29" s="1">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="F29" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G29" s="1">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -26213,7 +26280,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K29" s="5">
@@ -26221,163 +26288,163 @@
         <v>1</v>
       </c>
       <c r="M29" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="N29" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P29" s="1">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="Q29" s="9">
-        <v>12264732</v>
+        <v>12289475</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="S29" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B30" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="C30" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E30" s="1">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="F30" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G30" s="1">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I30" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J30" s="1">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0.97</v>
       </c>
       <c r="K30" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M30" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="N30" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="P30" s="1">
+        <v>400</v>
       </c>
       <c r="Q30" s="9">
-        <v>12264732</v>
+        <v>12289475</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="S30" s="1">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="C31" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E31" s="1">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="F31" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G31" s="1">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I31" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.18965517241379309</v>
       </c>
       <c r="J31" s="1">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0.81034482758620685</v>
       </c>
       <c r="K31" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.81034482758620685</v>
       </c>
       <c r="M31" s="4">
-        <v>46223</v>
+        <v>46234</v>
       </c>
       <c r="N31" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
+      </c>
+      <c r="O31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O31" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P31" s="1">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="Q31" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="S31" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="C32" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="E32" s="1">
+        <v>500</v>
       </c>
       <c r="F32" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G32" s="1">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -26387,7 +26454,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K32" s="5">
@@ -26395,511 +26462,511 @@
         <v>1</v>
       </c>
       <c r="M32" s="4">
-        <v>46223</v>
+        <v>46234</v>
       </c>
       <c r="N32" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
+      </c>
+      <c r="O32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O32" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P32" s="1">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="Q32" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="S32" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B33" s="4">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="C33" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
+      </c>
+      <c r="E33" s="1">
+        <v>600</v>
       </c>
       <c r="F33" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G33" s="1">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="H33" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I33" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>5.3191489361702128E-2</v>
       </c>
       <c r="J33" s="1">
-        <f>ABS(G$3-I33)</f>
-        <v>1</v>
+        <f t="shared" ref="J33:J37" si="4">ABS(G$3-I33)</f>
+        <v>0.94680851063829785</v>
       </c>
       <c r="K33" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.94680851063829785</v>
       </c>
       <c r="M33" s="4">
-        <v>46223</v>
+        <v>46234</v>
       </c>
       <c r="N33" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
+      </c>
+      <c r="O33" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O33" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P33" s="1">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="Q33" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S33" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
-        <v>46223</v>
+        <v>46234</v>
       </c>
       <c r="C34" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E34" s="1">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="F34" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G34" s="1">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I34" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>4.2553191489361701E-2</v>
       </c>
       <c r="J34" s="1">
-        <f t="shared" ref="J34:J44" si="3">ABS(G$3-I34)</f>
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>0.95744680851063835</v>
       </c>
       <c r="K34" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.95744680851063835</v>
       </c>
       <c r="M34" s="4">
-        <v>46223</v>
+        <v>46234</v>
       </c>
       <c r="N34" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O34" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P34" s="1">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="Q34" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="S34" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B35" s="4">
-        <v>46223</v>
+        <v>46234</v>
       </c>
       <c r="C35" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>31</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E35" s="1">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="F35" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G35" s="1">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="H35" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>1.4492753623188406E-2</v>
+        <v>0</v>
       </c>
       <c r="J35" s="1">
-        <f t="shared" si="3"/>
-        <v>0.98550724637681164</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="K35" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.98550724637681164</v>
+        <v>1</v>
       </c>
       <c r="M35" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="N35" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
+      </c>
+      <c r="O35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O35" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P35" s="1">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="Q35" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="S35" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B36" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="C36" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E36" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F36" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G36" s="1">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="H36" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I36" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>6.0606060606060608E-2</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="J36" s="1">
-        <f t="shared" si="3"/>
-        <v>0.93939393939393945</v>
+        <f t="shared" si="4"/>
+        <v>0.15384615384615385</v>
       </c>
       <c r="K36" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.93939393939393945</v>
+        <v>0.15384615384615385</v>
       </c>
       <c r="M36" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="N36" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
+      </c>
+      <c r="O36" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O36" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P36" s="1">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="Q36" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="S36" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B37" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="C37" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E37" s="1">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F37" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G37" s="1">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="H37" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I37" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="J37" s="1">
-        <f t="shared" si="3"/>
-        <v>0.52</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="K37" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.52</v>
+        <v>1</v>
       </c>
       <c r="M37" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="N37" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
+      </c>
+      <c r="O37" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O37" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P37" s="1">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="Q37" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="S37" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B38" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="C38" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E38" s="1">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="F38" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G38" s="1">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H38" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I38" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.11428571428571428</v>
+        <v>0</v>
       </c>
       <c r="J38" s="1">
-        <f t="shared" si="3"/>
-        <v>0.88571428571428568</v>
+        <f t="shared" ref="J38:J45" si="5">ABS(G$3-I38)</f>
+        <v>1</v>
       </c>
       <c r="K38" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.88571428571428568</v>
+        <v>1</v>
       </c>
       <c r="M38" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="N38" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
+      </c>
+      <c r="O38" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O38" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P38" s="1">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="Q38" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S38" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B39" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="C39" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E39" s="1">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="F39" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G39" s="1">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H39" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I39" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.25714285714285712</v>
+        <v>0</v>
       </c>
       <c r="J39" s="1">
-        <f t="shared" si="3"/>
-        <v>0.74285714285714288</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="K39" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.74285714285714288</v>
+        <v>1</v>
       </c>
       <c r="M39" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="N39" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
+      </c>
+      <c r="O39" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O39" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P39" s="1">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="Q39" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="S39" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B40" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="C40" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E40" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="F40" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G40" s="1">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H40" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I40" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J40" s="1">
-        <f t="shared" si="3"/>
-        <v>0.6</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="K40" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M40" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="N40" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
+      </c>
+      <c r="O40" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O40" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P40" s="1">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="Q40" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="S40" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="C41" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E41" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="F41" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G41" s="1">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
@@ -26909,7 +26976,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K41" s="5">
@@ -26917,47 +26984,47 @@
         <v>1</v>
       </c>
       <c r="M41" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="N41" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
+      </c>
+      <c r="O41" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O41" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="P41" s="1">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="Q41" s="9">
-        <v>12264714</v>
+        <v>12289497</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="S41" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B42" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="C42" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>15</v>
+      <c r="E42" s="1">
+        <v>700</v>
       </c>
       <c r="F42" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G42" s="1">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -26967,7 +27034,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K42" s="5">
@@ -26975,47 +27042,47 @@
         <v>1</v>
       </c>
       <c r="M42" s="4">
-        <v>46223</v>
+        <v>46232</v>
       </c>
       <c r="N42" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P42" s="1">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="Q42" s="9">
-        <v>12264714</v>
+        <v>10532587</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="S42" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B43" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="C43" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>17</v>
+      <c r="E43" s="1">
+        <v>800</v>
       </c>
       <c r="F43" s="9">
-        <v>12264714</v>
+        <v>12289475</v>
       </c>
       <c r="G43" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -27025,7 +27092,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K43" s="5">
@@ -27033,255 +27100,255 @@
         <v>1</v>
       </c>
       <c r="M43" s="4">
-        <v>46223</v>
+        <v>46232</v>
       </c>
       <c r="N43" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P43" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q43" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S43" s="1">
         <v>18</v>
-      </c>
-      <c r="P43" s="1">
-        <v>800</v>
-      </c>
-      <c r="Q43" s="9">
-        <v>12264714</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S43" s="1">
-        <v>14</v>
       </c>
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
-        <v>46227</v>
+        <v>46238</v>
       </c>
       <c r="C44" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="E44" s="1">
         <v>100</v>
       </c>
       <c r="F44" s="9">
-        <v>12260416</v>
+        <v>12289497</v>
       </c>
       <c r="G44" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H44" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I44" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J44" s="1">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.5</v>
       </c>
       <c r="K44" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M44" s="4">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="N44" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P44" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q44" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="S44" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B45" s="4">
-        <v>46227</v>
+        <v>46238</v>
       </c>
       <c r="C45" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="E45" s="1">
         <v>200</v>
       </c>
       <c r="F45" s="9">
-        <v>12260416</v>
+        <v>12289497</v>
       </c>
       <c r="G45" s="1">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H45" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I45" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.04</v>
+        <v>0.21428571428571427</v>
       </c>
       <c r="J45" s="1">
-        <f t="shared" ref="J45:J52" si="4">ABS(G$3-I45)</f>
-        <v>0.96</v>
+        <f t="shared" si="5"/>
+        <v>0.7857142857142857</v>
       </c>
       <c r="K45" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.96</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="M45" s="4">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="N45" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P45" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q45" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="S45" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B46" s="4">
-        <v>46227</v>
+        <v>46238</v>
       </c>
       <c r="C46" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="E46" s="1">
         <v>300</v>
       </c>
       <c r="F46" s="9">
-        <v>12260416</v>
+        <v>12289497</v>
       </c>
       <c r="G46" s="1">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="H46" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I46" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="J46" s="1">
-        <f t="shared" si="4"/>
-        <v>0.75</v>
+        <f t="shared" ref="J46:J51" si="6">ABS(G$3-I46)</f>
+        <v>1</v>
       </c>
       <c r="K46" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M46" s="4">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="N46" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P46" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q46" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="S46" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
-        <v>46227</v>
+        <v>46238</v>
       </c>
       <c r="C47" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="E47" s="1">
         <v>400</v>
       </c>
       <c r="F47" s="9">
-        <v>12260416</v>
+        <v>12289497</v>
       </c>
       <c r="G47" s="1">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="H47" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J47" s="1">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="K47" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M47" s="4">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="N47" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P47" s="1">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Q47" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="S47" s="1">
         <v>6</v>
@@ -27289,197 +27356,197 @@
     </row>
     <row r="48" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
-        <v>46227</v>
+        <v>46238</v>
       </c>
       <c r="C48" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E48" s="1">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F48" s="9">
-        <v>12260416</v>
+        <v>12289497</v>
       </c>
       <c r="G48" s="1">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="H48" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I48" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.2</v>
+        <v>0.11904761904761904</v>
       </c>
       <c r="J48" s="1">
-        <f t="shared" si="4"/>
-        <v>0.8</v>
+        <f t="shared" si="6"/>
+        <v>0.88095238095238093</v>
       </c>
       <c r="K48" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.8</v>
+        <v>0.88095238095238093</v>
       </c>
       <c r="M48" s="4">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="N48" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P48" s="1">
-        <v>400</v>
+        <v>15</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q48" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="S48" s="1">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B49" s="4">
-        <v>46227</v>
+        <v>46238</v>
       </c>
       <c r="C49" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E49" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F49" s="9">
-        <v>12260416</v>
+        <v>12289497</v>
       </c>
       <c r="G49" s="1">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="H49" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.69230769230769229</v>
+        <v>0</v>
       </c>
       <c r="J49" s="1">
-        <f t="shared" si="4"/>
-        <v>0.30769230769230771</v>
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="K49" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.30769230769230771</v>
+        <v>1</v>
       </c>
       <c r="M49" s="4">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="N49" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P49" s="1">
-        <v>400</v>
+        <v>15</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q49" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S49" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B50" s="4">
-        <v>46227</v>
+        <v>46238</v>
       </c>
       <c r="C50" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E50" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F50" s="9">
-        <v>12260416</v>
+        <v>12289497</v>
       </c>
       <c r="G50" s="1">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H50" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I50" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>5.2631578947368418E-2</v>
+        <v>0</v>
       </c>
       <c r="J50" s="1">
-        <f t="shared" si="4"/>
-        <v>0.94736842105263164</v>
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="K50" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.94736842105263164</v>
+        <v>1</v>
       </c>
       <c r="M50" s="4">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="N50" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P50" s="1">
-        <v>400</v>
+        <v>15</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q50" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="S50" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B51" s="4">
-        <v>46227</v>
+        <v>46238</v>
       </c>
       <c r="C51" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E51" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F51" s="9">
-        <v>12260416</v>
+        <v>12289497</v>
       </c>
       <c r="G51" s="1">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
@@ -27489,7 +27556,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K51" s="5">
@@ -27497,337 +27564,337 @@
         <v>1</v>
       </c>
       <c r="M51" s="4">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="N51" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>31</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P51" s="1">
-        <v>400</v>
+        <v>15</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q51" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="S51" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B52" s="4">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="C52" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E52" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="E52" s="1">
+        <v>100</v>
+      </c>
       <c r="F52" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="G52" s="1">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="H52" s="1">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="I52" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.1875</v>
+        <v>0.25833333333333336</v>
       </c>
       <c r="J52" s="1">
-        <f t="shared" si="4"/>
-        <v>0.8125</v>
+        <f t="shared" ref="J52:J60" si="7">ABS(G$3-I52)</f>
+        <v>0.7416666666666667</v>
       </c>
       <c r="K52" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.8125</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="M52" s="4">
-        <v>46227</v>
+        <v>46239</v>
       </c>
       <c r="N52" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P52" s="1">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="Q52" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="S52" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B53" s="4">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="C53" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="E53" s="1">
+        <v>150</v>
       </c>
       <c r="F53" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="G53" s="1">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="H53" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I53" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>8.5714285714285715E-2</v>
       </c>
       <c r="J53" s="1">
-        <f>ABS(G$3-I53)</f>
-        <v>1</v>
+        <f t="shared" si="7"/>
+        <v>0.91428571428571426</v>
       </c>
       <c r="K53" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.91428571428571426</v>
       </c>
       <c r="M53" s="4">
-        <v>46227</v>
+        <v>46239</v>
       </c>
       <c r="N53" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P53" s="1">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="Q53" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="S53" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B54" s="4">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="C54" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E54" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F54" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G54" s="1">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="H54" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I54" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.15238095238095239</v>
       </c>
       <c r="J54" s="1">
-        <f t="shared" ref="J54:J61" si="5">ABS(G$3-I54)</f>
-        <v>1</v>
+        <f t="shared" si="7"/>
+        <v>0.84761904761904761</v>
       </c>
       <c r="K54" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.84761904761904761</v>
       </c>
       <c r="M54" s="4">
-        <v>46227</v>
+        <v>46239</v>
       </c>
       <c r="N54" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
       </c>
       <c r="O54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P54" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q54" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S54" s="1">
         <v>18</v>
-      </c>
-      <c r="P54" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q54" s="9">
-        <v>12260416</v>
-      </c>
-      <c r="R54" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="S54" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="55" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B55" s="4">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="C55" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E55" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F55" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G55" s="1">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="H55" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I55" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>5.9405940594059403E-2</v>
       </c>
       <c r="J55" s="1">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f t="shared" si="7"/>
+        <v>0.94059405940594054</v>
       </c>
       <c r="K55" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.94059405940594054</v>
       </c>
       <c r="M55" s="4">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="N55" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P55" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="P55" s="1">
+        <v>300</v>
+      </c>
       <c r="Q55" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S55" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="C56" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E56" s="1">
-        <v>300</v>
+        <v>15</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F56" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G56" s="1">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="H56" s="1">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I56" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.7068965517241379</v>
       </c>
       <c r="J56" s="1">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f t="shared" si="7"/>
+        <v>0.2931034482758621</v>
       </c>
       <c r="K56" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.2931034482758621</v>
       </c>
       <c r="M56" s="4">
-        <v>46227</v>
+        <v>46239</v>
       </c>
       <c r="N56" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P56" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="P56" s="1">
+        <v>300</v>
+      </c>
       <c r="Q56" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="S56" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B57" s="4">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="C57" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E57" s="1">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F57" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G57" s="1">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
@@ -27837,7 +27904,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K57" s="5">
@@ -27845,313 +27912,313 @@
         <v>1</v>
       </c>
       <c r="M57" s="4">
-        <v>46227</v>
+        <v>46239</v>
       </c>
       <c r="N57" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P57" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="P57" s="1">
+        <v>300</v>
+      </c>
       <c r="Q57" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R57" s="1" t="s">
         <v>48</v>
       </c>
       <c r="S57" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B58" s="4">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="C58" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E58" s="1">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="F58" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G58" s="1">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="H58" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.15789473684210525</v>
+        <v>0</v>
       </c>
       <c r="J58" s="1">
-        <f t="shared" si="5"/>
-        <v>0.84210526315789469</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="K58" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.84210526315789469</v>
+        <v>1</v>
       </c>
       <c r="M58" s="4">
-        <v>46220</v>
+        <v>46237</v>
       </c>
       <c r="N58" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>29</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q58" s="9">
-        <v>12264714</v>
+        <v>10532587</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="S58" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B59" s="4">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="C59" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E59" s="1">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="F59" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G59" s="1">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="H59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>5.5555555555555552E-2</v>
+        <v>0</v>
       </c>
       <c r="J59" s="1">
-        <f t="shared" si="5"/>
-        <v>0.94444444444444442</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="K59" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.94444444444444442</v>
+        <v>1</v>
       </c>
       <c r="M59" s="4">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="N59" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P59" s="1">
-        <v>600</v>
+        <v>15</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q59" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="S59" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B60" s="4">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="C60" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E60" s="1">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="F60" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G60" s="1">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="H60" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I60" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.22222222222222221</v>
+        <v>3.4482758620689655E-2</v>
       </c>
       <c r="J60" s="1">
-        <f t="shared" si="5"/>
-        <v>0.77777777777777779</v>
+        <f t="shared" si="7"/>
+        <v>0.96551724137931039</v>
       </c>
       <c r="K60" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.77777777777777779</v>
+        <v>0.96551724137931039</v>
       </c>
       <c r="M60" s="4">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="N60" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P60" s="1">
-        <v>700</v>
+        <v>15</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q60" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S60" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="C61" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E61" s="1">
-        <v>900</v>
+        <v>15</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F61" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G61" s="1">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="H61" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I61" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="J61" s="1">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f>ABS(G$3-I61)</f>
+        <v>0.84</v>
       </c>
       <c r="K61" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="M61" s="4">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="N61" s="1">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P61" s="1">
-        <v>800</v>
+        <v>15</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q61" s="9">
-        <v>12260416</v>
+        <v>10532587</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="S61" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
-        <v>46227</v>
+        <v>46239</v>
       </c>
       <c r="C62" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="E62" s="1">
+        <v>100</v>
+      </c>
       <c r="F62" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="G62" s="1">
-        <v>40</v>
+        <v>219</v>
       </c>
       <c r="H62" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I62" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
+        <v>6.3926940639269403E-2</v>
       </c>
       <c r="J62" s="1">
-        <f t="shared" ref="J62" si="6">ABS(G$3-I62)</f>
-        <v>1</v>
+        <f t="shared" ref="J62:J66" si="8">ABS(G$3-I62)</f>
+        <v>0.9360730593607306</v>
       </c>
       <c r="K62" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.9360730593607306</v>
       </c>
       <c r="M62" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N62" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>36</v>
+        <v>46237</v>
+      </c>
+      <c r="N62" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P62" s="1">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="Q62" s="9">
-        <v>12260415</v>
+        <v>10532587</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="S62" s="1">
         <v>1</v>
@@ -28159,1125 +28226,1125 @@
     </row>
     <row r="63" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C63" s="12">
+        <v>46239</v>
+      </c>
+      <c r="C63" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" s="1">
+        <v>150</v>
+      </c>
+      <c r="F63" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G63" s="1">
+        <v>219</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="1">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K63" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M63" s="4">
+        <v>46237</v>
+      </c>
+      <c r="N63" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P63" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q63" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R63" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S63" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B64" s="4">
+        <v>46239</v>
+      </c>
+      <c r="C64" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" s="1">
+        <v>200</v>
+      </c>
+      <c r="F64" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G64" s="1">
+        <v>216</v>
+      </c>
+      <c r="H64" s="1">
+        <v>18</v>
+      </c>
+      <c r="I64" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="J64" s="1">
+        <f t="shared" si="8"/>
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="K64" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="M64" s="4">
+        <v>46239</v>
+      </c>
+      <c r="N64" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q64" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R64" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S64" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B65" s="4">
+        <v>46239</v>
+      </c>
+      <c r="C65" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" s="1">
+        <v>300</v>
+      </c>
+      <c r="F65" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G65" s="1">
+        <v>210</v>
+      </c>
+      <c r="H65" s="1">
+        <v>8</v>
+      </c>
+      <c r="I65" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>3.8095238095238099E-2</v>
+      </c>
+      <c r="J65" s="1">
+        <f t="shared" si="8"/>
+        <v>0.96190476190476193</v>
+      </c>
+      <c r="K65" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.96190476190476193</v>
+      </c>
+      <c r="M65" s="4">
+        <v>46239</v>
+      </c>
+      <c r="N65" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q65" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R65" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S65" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B66" s="4">
+        <v>46239</v>
+      </c>
+      <c r="C66" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>32</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F66" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="G66" s="1">
+        <v>187</v>
+      </c>
+      <c r="H66" s="1">
+        <v>24</v>
+      </c>
+      <c r="I66" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.12834224598930483</v>
+      </c>
+      <c r="J66" s="1">
+        <f t="shared" si="8"/>
+        <v>0.87165775401069512</v>
+      </c>
+      <c r="K66" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.87165775401069512</v>
+      </c>
+      <c r="M66" s="4">
+        <v>46239</v>
+      </c>
+      <c r="N66" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>32</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q66" s="9">
+        <v>10532587</v>
+      </c>
+      <c r="R66" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S66" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B67" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C67" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E63" s="1">
+      <c r="D67" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E67" s="1">
         <v>100</v>
       </c>
-      <c r="F63" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="G63" s="1">
-        <v>100</v>
-      </c>
-      <c r="H63" s="1">
+      <c r="F67" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G67" s="1">
+        <v>15</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0</v>
+      </c>
+      <c r="I67" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="1">
+        <f t="shared" ref="J67:J75" si="9">ABS(G$3-I67)</f>
         <v>1</v>
       </c>
-      <c r="I63" s="3">
-        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.01</v>
-      </c>
-      <c r="J63" s="12">
-        <f t="shared" ref="J63:J71" si="7">ABS(G$3-I63)</f>
-        <v>0.99</v>
-      </c>
-      <c r="K63" s="5">
+      <c r="K67" s="11">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.99</v>
-      </c>
-      <c r="M63" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N63" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>1</v>
+      </c>
+      <c r="M67" s="4">
+        <v>46269</v>
+      </c>
+      <c r="N67" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>36</v>
       </c>
-      <c r="O63" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P63" s="1">
-        <v>100</v>
-      </c>
-      <c r="Q63" s="9">
-        <v>12260416</v>
-      </c>
-      <c r="R63" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="S63" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B64" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C64" s="12">
+      <c r="O67" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P67" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S67" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B68" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C68" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E64" s="1">
+      <c r="D68" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" s="1">
         <v>200</v>
       </c>
-      <c r="F64" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="G64" s="1">
-        <v>80</v>
-      </c>
-      <c r="H64" s="1">
+      <c r="F68" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G68" s="1">
+        <v>15</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+      <c r="I68" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J68" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="I64" s="3">
-        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="J64" s="12">
-        <f t="shared" si="7"/>
-        <v>0.98750000000000004</v>
-      </c>
-      <c r="K64" s="5">
+      <c r="K68" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.98750000000000004</v>
-      </c>
-      <c r="M64" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N64" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>1</v>
+      </c>
+      <c r="M68" s="4">
+        <v>46269</v>
+      </c>
+      <c r="N68" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>36</v>
       </c>
-      <c r="O64" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P64" s="1">
-        <v>200</v>
-      </c>
-      <c r="Q64" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="R64" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S64" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B65" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C65" s="12">
+      <c r="O68" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P68" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q68" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R68" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S68" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B69" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C69" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E65" s="1">
+      <c r="D69" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E69" s="1">
         <v>300</v>
       </c>
-      <c r="F65" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="G65" s="1">
-        <v>81</v>
-      </c>
-      <c r="H65" s="1">
-        <v>3</v>
-      </c>
-      <c r="I65" s="3">
+      <c r="F69" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G69" s="1">
+        <v>15</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+      <c r="I69" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>3.7037037037037035E-2</v>
-      </c>
-      <c r="J65" s="12">
-        <f t="shared" si="7"/>
-        <v>0.96296296296296302</v>
-      </c>
-      <c r="K65" s="5">
+        <v>0</v>
+      </c>
+      <c r="J69" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="K69" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.96296296296296302</v>
-      </c>
-      <c r="M65" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N65" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>1</v>
+      </c>
+      <c r="M69" s="4">
+        <v>46269</v>
+      </c>
+      <c r="N69" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>36</v>
       </c>
-      <c r="O65" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P65" s="1">
-        <v>200</v>
-      </c>
-      <c r="Q65" s="9">
-        <v>12260416</v>
-      </c>
-      <c r="R65" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="S65" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B66" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C66" s="12">
+      <c r="O69" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P69" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q69" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R69" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="S69" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B70" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C70" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E66" s="1">
+      <c r="D70" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E70" s="1">
         <v>400</v>
       </c>
-      <c r="F66" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="G66" s="1">
-        <v>80</v>
-      </c>
-      <c r="H66" s="1">
-        <v>7</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="F70" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G70" s="1">
+        <v>15</v>
+      </c>
+      <c r="H70" s="1">
+        <v>6</v>
+      </c>
+      <c r="I70" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="J66" s="12">
-        <f t="shared" si="7"/>
-        <v>0.91249999999999998</v>
-      </c>
-      <c r="K66" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="J70" s="1">
+        <f t="shared" si="9"/>
+        <v>0.6</v>
+      </c>
+      <c r="K70" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.91249999999999998</v>
-      </c>
-      <c r="M66" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N66" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>0.6</v>
+      </c>
+      <c r="M70" s="4">
+        <v>46269</v>
+      </c>
+      <c r="N70" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>36</v>
       </c>
-      <c r="O66" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P66" s="1">
-        <v>300</v>
-      </c>
-      <c r="Q66" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="R66" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S66" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B67" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C67" s="12">
+      <c r="O70" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P70" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q70" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="S70" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B71" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C71" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E67" s="1">
-        <v>600</v>
-      </c>
-      <c r="F67" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="G67" s="1">
-        <v>75</v>
-      </c>
-      <c r="H67" s="1">
-        <v>3</v>
-      </c>
-      <c r="I67" s="3">
+      <c r="D71" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E71" s="1">
+        <v>500</v>
+      </c>
+      <c r="F71" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G71" s="1">
+        <v>15</v>
+      </c>
+      <c r="H71" s="1">
+        <v>0</v>
+      </c>
+      <c r="I71" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.04</v>
-      </c>
-      <c r="J67" s="12">
-        <f t="shared" si="7"/>
-        <v>0.96</v>
-      </c>
-      <c r="K67" s="5">
+        <v>0</v>
+      </c>
+      <c r="J71" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="K71" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.96</v>
-      </c>
-      <c r="M67" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N67" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>36</v>
-      </c>
-      <c r="O67" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P67" s="1">
-        <v>300</v>
-      </c>
-      <c r="Q67" s="9">
-        <v>12260416</v>
-      </c>
-      <c r="R67" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S67" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B68" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C68" s="12">
+      <c r="M71" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N71" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P71" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q71" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R71" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="S71" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B72" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C72" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E68" s="1">
-        <v>700</v>
-      </c>
-      <c r="F68" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="G68" s="1">
-        <v>75</v>
-      </c>
-      <c r="H68" s="1">
-        <v>2</v>
-      </c>
-      <c r="I68" s="3">
+      <c r="D72" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E72" s="1">
+        <v>600</v>
+      </c>
+      <c r="F72" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G72" s="1">
+        <v>15</v>
+      </c>
+      <c r="H72" s="1">
+        <v>6</v>
+      </c>
+      <c r="I72" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>2.6666666666666668E-2</v>
-      </c>
-      <c r="J68" s="12">
-        <f t="shared" si="7"/>
-        <v>0.97333333333333338</v>
-      </c>
-      <c r="K68" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="J72" s="1">
+        <f t="shared" si="9"/>
+        <v>0.6</v>
+      </c>
+      <c r="K72" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.97333333333333338</v>
-      </c>
-      <c r="M68" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N68" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>36</v>
-      </c>
-      <c r="O68" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P68" s="1">
-        <v>400</v>
-      </c>
-      <c r="Q68" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="R68" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S68" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B69" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C69" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="M72" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N72" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P72" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q72" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R72" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S72" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B73" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C73" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E69" s="1">
-        <v>800</v>
-      </c>
-      <c r="F69" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="G69" s="1">
+      <c r="D73" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E73" s="1">
+        <v>700</v>
+      </c>
+      <c r="F73" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G73" s="1">
+        <v>15</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0</v>
+      </c>
+      <c r="I73" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J73" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="K73" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M73" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N73" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
         <v>37</v>
       </c>
-      <c r="H69" s="1">
-        <v>17</v>
-      </c>
-      <c r="I69" s="3">
-        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.45945945945945948</v>
-      </c>
-      <c r="J69" s="12">
-        <f t="shared" si="7"/>
-        <v>0.54054054054054057</v>
-      </c>
-      <c r="K69" s="5">
-        <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.54054054054054057</v>
-      </c>
-      <c r="M69" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N69" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>36</v>
-      </c>
-      <c r="O69" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P69" s="1">
+      <c r="O73" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P73" s="1">
         <v>400</v>
       </c>
-      <c r="Q69" s="9">
-        <v>12260416</v>
-      </c>
-      <c r="R69" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S69" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B70" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C70" s="12">
+      <c r="Q73" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R73" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S73" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B74" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C74" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E70" s="1">
-        <v>900</v>
-      </c>
-      <c r="F70" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="G70" s="1">
-        <v>57</v>
-      </c>
-      <c r="H70" s="1">
-        <v>5</v>
-      </c>
-      <c r="I70" s="3">
+      <c r="D74" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E74" s="1">
+        <v>800</v>
+      </c>
+      <c r="F74" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G74" s="1">
+        <v>15</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0</v>
+      </c>
+      <c r="I74" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>8.771929824561403E-2</v>
-      </c>
-      <c r="J70" s="12">
-        <f t="shared" si="7"/>
-        <v>0.91228070175438591</v>
-      </c>
-      <c r="K70" s="5">
+        <v>0</v>
+      </c>
+      <c r="J74" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="K74" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.91228070175438591</v>
-      </c>
-      <c r="M70" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N70" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>36</v>
-      </c>
-      <c r="O70" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P70" s="1">
-        <v>400</v>
-      </c>
-      <c r="Q70" s="9">
-        <v>12260416</v>
-      </c>
-      <c r="R70" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="S70" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B71" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C71" s="12">
+      <c r="M74" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N74" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P74" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q74" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R74" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="S74" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B75" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C75" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E71" s="1" t="s">
+      <c r="D75" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F75" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G75" s="1">
         <v>15</v>
       </c>
-      <c r="F71" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="G71" s="1">
-        <v>57</v>
-      </c>
-      <c r="H71" s="1">
-        <v>3</v>
-      </c>
-      <c r="I71" s="3">
+      <c r="H75" s="1">
+        <v>0</v>
+      </c>
+      <c r="I75" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>5.2631578947368418E-2</v>
-      </c>
-      <c r="J71" s="12">
-        <f t="shared" si="7"/>
-        <v>0.94736842105263164</v>
-      </c>
-      <c r="K71" s="5">
+        <v>0</v>
+      </c>
+      <c r="J75" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="K75" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.94736842105263164</v>
-      </c>
-      <c r="M71" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N71" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>36</v>
-      </c>
-      <c r="O71" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P71" s="1">
+        <v>1</v>
+      </c>
+      <c r="M75" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N75" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P75" s="1">
         <v>600</v>
       </c>
-      <c r="Q71" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="R71" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="S71" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B72" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C72" s="12">
+      <c r="Q75" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R75" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S75" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B76" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C76" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
         <v>36</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F72" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="G72" s="1">
-        <v>57</v>
-      </c>
-      <c r="H72" s="1">
+      <c r="D76" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F76" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G76" s="1">
+        <v>14</v>
+      </c>
+      <c r="H76" s="1">
+        <v>9</v>
+      </c>
+      <c r="I76" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="J76" s="1">
+        <f>ABS(G$3-I76)</f>
+        <v>0.3571428571428571</v>
+      </c>
+      <c r="K76" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.3571428571428571</v>
+      </c>
+      <c r="M76" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N76" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P76" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q76" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R76" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="S76" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B77" s="4">
+        <v>46269</v>
+      </c>
+      <c r="C77" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>36</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F77" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G77" s="1">
+        <v>15</v>
+      </c>
+      <c r="H77" s="1">
         <v>0</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I77" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J72" s="12">
-        <f t="shared" ref="J72:J75" si="8">ABS(G$3-I72)</f>
+      <c r="J77" s="1">
+        <f>ABS(G$3-I77)</f>
         <v>1</v>
       </c>
-      <c r="K72" s="5">
+      <c r="K77" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
         <v>1</v>
       </c>
-      <c r="M72" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N72" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>36</v>
-      </c>
-      <c r="O72" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P72" s="1">
-        <v>600</v>
-      </c>
-      <c r="Q72" s="9">
-        <v>12260416</v>
-      </c>
-      <c r="R72" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="S72" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B73" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C73" s="12">
-        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>36</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E73" s="1">
-        <v>100</v>
-      </c>
-      <c r="F73" s="9">
-        <v>12260416</v>
-      </c>
-      <c r="G73" s="1">
-        <v>139</v>
-      </c>
-      <c r="H73" s="1">
-        <v>1</v>
-      </c>
-      <c r="I73" s="3">
-        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>7.1942446043165471E-3</v>
-      </c>
-      <c r="J73" s="12">
-        <f t="shared" si="8"/>
-        <v>0.9928057553956835</v>
-      </c>
-      <c r="K73" s="5">
-        <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.9928057553956835</v>
-      </c>
-      <c r="M73" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N73" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>36</v>
-      </c>
-      <c r="O73" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P73" s="1">
+      <c r="M77" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N77" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P77" s="1">
         <v>700</v>
       </c>
-      <c r="Q73" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="R73" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="S73" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B74" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C74" s="12">
-        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>36</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E74" s="1">
-        <v>200</v>
-      </c>
-      <c r="F74" s="9">
-        <v>12260416</v>
-      </c>
-      <c r="G74" s="1">
-        <v>137</v>
-      </c>
-      <c r="H74" s="1">
-        <v>4</v>
-      </c>
-      <c r="I74" s="3">
-        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>2.9197080291970802E-2</v>
-      </c>
-      <c r="J74" s="12">
-        <f t="shared" si="8"/>
-        <v>0.97080291970802923</v>
-      </c>
-      <c r="K74" s="5">
-        <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.97080291970802923</v>
-      </c>
-      <c r="M74" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N74" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>36</v>
-      </c>
-      <c r="O74" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P74" s="1">
-        <v>700</v>
-      </c>
-      <c r="Q74" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="R74" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="S74" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B75" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C75" s="12">
-        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>36</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E75" s="1">
-        <v>300</v>
-      </c>
-      <c r="F75" s="9">
-        <v>12260416</v>
-      </c>
-      <c r="G75" s="1">
-        <v>134</v>
-      </c>
-      <c r="H75" s="1">
-        <v>1</v>
-      </c>
-      <c r="I75" s="3">
-        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>7.462686567164179E-3</v>
-      </c>
-      <c r="J75" s="12">
-        <f t="shared" si="8"/>
-        <v>0.9925373134328358</v>
-      </c>
-      <c r="K75" s="5">
-        <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.9925373134328358</v>
-      </c>
-      <c r="M75" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N75" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>36</v>
-      </c>
-      <c r="O75" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P75" s="1">
-        <v>700</v>
-      </c>
-      <c r="Q75" s="9">
-        <v>12260416</v>
-      </c>
-      <c r="R75" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="S75" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B76" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C76" s="12">
-        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>36</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E76" s="1">
-        <v>400</v>
-      </c>
-      <c r="F76" s="9">
-        <v>12260416</v>
-      </c>
-      <c r="G76" s="1">
-        <v>125</v>
-      </c>
-      <c r="H76" s="1">
-        <v>5</v>
-      </c>
-      <c r="I76" s="3">
-        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0.04</v>
-      </c>
-      <c r="J76" s="12">
-        <f t="shared" ref="J76:J82" si="9">ABS(G$3-I76)</f>
-        <v>0.96</v>
-      </c>
-      <c r="K76" s="5">
-        <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.96</v>
-      </c>
-      <c r="M76" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N76" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>36</v>
-      </c>
-      <c r="O76" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P76" s="1">
-        <v>800</v>
-      </c>
-      <c r="Q76" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="R76" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S76" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B77" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C77" s="12">
-        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>36</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E77" s="1">
-        <v>600</v>
-      </c>
-      <c r="F77" s="9">
-        <v>12260416</v>
-      </c>
-      <c r="G77" s="1">
-        <v>128</v>
-      </c>
-      <c r="H77" s="1">
-        <v>1</v>
-      </c>
-      <c r="I77" s="3">
-        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>7.8125E-3</v>
-      </c>
-      <c r="J77" s="12">
-        <f t="shared" si="9"/>
-        <v>0.9921875</v>
-      </c>
-      <c r="K77" s="5">
-        <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.9921875</v>
-      </c>
-      <c r="M77" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N77" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>36</v>
-      </c>
-      <c r="O77" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P77" s="1">
-        <v>800</v>
-      </c>
       <c r="Q77" s="9">
-        <v>12260415</v>
+        <v>12289507</v>
       </c>
       <c r="R77" s="1" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="S77" s="1">
-        <v>4</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C78" s="12">
+        <v>46272</v>
+      </c>
+      <c r="C78" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E78" s="1">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="F78" s="9">
-        <v>12260416</v>
+        <v>12289507</v>
       </c>
       <c r="G78" s="1">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="H78" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I78" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>1.6393442622950821E-2</v>
-      </c>
-      <c r="J78" s="12">
-        <f t="shared" si="9"/>
-        <v>0.98360655737704916</v>
+        <v>0</v>
+      </c>
+      <c r="J78" s="1">
+        <f t="shared" ref="J78:J82" si="10">ABS(G$3-I78)</f>
+        <v>1</v>
       </c>
       <c r="K78" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.98360655737704916</v>
+        <v>1</v>
       </c>
       <c r="M78" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N78" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>36</v>
+        <v>46272</v>
+      </c>
+      <c r="N78" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P78" s="1">
         <v>800</v>
       </c>
       <c r="Q78" s="9">
-        <v>12260415</v>
+        <v>12289507</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="S78" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B79" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C79" s="12">
+        <v>46272</v>
+      </c>
+      <c r="C79" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E79" s="1">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="F79" s="9">
-        <v>12260416</v>
+        <v>12289507</v>
       </c>
       <c r="G79" s="1">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H79" s="1">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I79" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>2.197802197802198E-2</v>
-      </c>
-      <c r="J79" s="12">
-        <f t="shared" si="9"/>
-        <v>0.97802197802197799</v>
+        <v>0.14563106796116504</v>
+      </c>
+      <c r="J79" s="1">
+        <f t="shared" si="10"/>
+        <v>0.85436893203883502</v>
       </c>
       <c r="K79" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.97802197802197799</v>
+        <v>0.85436893203883502</v>
       </c>
       <c r="M79" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N79" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>36</v>
+        <v>46272</v>
+      </c>
+      <c r="N79" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P79" s="1">
-        <v>800</v>
+        <v>30</v>
+      </c>
+      <c r="P79" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="Q79" s="9">
-        <v>12260416</v>
+        <v>12289507</v>
       </c>
       <c r="R79" s="1" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="S79" s="1">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B80" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C80" s="12">
+        <v>46272</v>
+      </c>
+      <c r="C80" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E80" s="1">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="F80" s="9">
-        <v>12260416</v>
+        <v>12289507</v>
       </c>
       <c r="G80" s="1">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H80" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I80" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>5.8823529411764705E-2</v>
-      </c>
-      <c r="J80" s="12">
-        <f t="shared" si="9"/>
-        <v>0.94117647058823528</v>
+        <v>2.9126213592233011E-2</v>
+      </c>
+      <c r="J80" s="1">
+        <f t="shared" si="10"/>
+        <v>0.970873786407767</v>
       </c>
       <c r="K80" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>0.94117647058823528</v>
+        <v>0.970873786407767</v>
       </c>
       <c r="M80" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N80" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>36</v>
+        <v>46272</v>
+      </c>
+      <c r="N80" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P80" s="1">
-        <v>900</v>
+        <v>30</v>
+      </c>
+      <c r="P80" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="Q80" s="9">
-        <v>12260415</v>
+        <v>12289507</v>
       </c>
       <c r="R80" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="S80" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B81" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C81" s="12">
+        <v>46272</v>
+      </c>
+      <c r="C81" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="E81" s="1">
+        <v>400</v>
       </c>
       <c r="F81" s="9">
-        <v>12260416</v>
+        <v>12289507</v>
       </c>
       <c r="G81" s="1">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H81" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I81" s="3">
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
-        <v>0</v>
-      </c>
-      <c r="J81" s="12">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.9417475728155338E-2</v>
+      </c>
+      <c r="J81" s="1">
+        <f t="shared" si="10"/>
+        <v>0.98058252427184467</v>
       </c>
       <c r="K81" s="5">
         <f>Tabla158[[#This Row],[FTQ]]</f>
-        <v>1</v>
+        <v>0.98058252427184467</v>
       </c>
       <c r="M81" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N81" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>36</v>
+        <v>46272</v>
+      </c>
+      <c r="N81" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P81" s="1">
-        <v>900</v>
+        <v>30</v>
+      </c>
+      <c r="P81" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="Q81" s="9">
-        <v>12260416</v>
+        <v>12289507</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="S81" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B82" s="4">
-        <v>46265</v>
-      </c>
-      <c r="C82" s="12">
+        <v>46272</v>
+      </c>
+      <c r="C82" s="1">
         <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>51</v>
+        <v>30</v>
+      </c>
+      <c r="E82" s="1">
+        <v>500</v>
       </c>
       <c r="F82" s="9">
-        <v>12260416</v>
+        <v>12289507</v>
       </c>
       <c r="G82" s="1">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H82" s="1">
         <v>0</v>
@@ -29286,8 +29353,8 @@
         <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
         <v>0</v>
       </c>
-      <c r="J82" s="12">
-        <f t="shared" si="9"/>
+      <c r="J82" s="1">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K82" s="5">
@@ -29295,159 +29362,893 @@
         <v>1</v>
       </c>
       <c r="M82" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N82" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
+        <v>46272</v>
+      </c>
+      <c r="N82" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P82" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q82" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R82" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="S82" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B83" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C83" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E83" s="1">
+        <v>600</v>
+      </c>
+      <c r="F83" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G83" s="1">
+        <v>101</v>
+      </c>
+      <c r="H83" s="1">
+        <v>80</v>
+      </c>
+      <c r="I83" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.79207920792079212</v>
+      </c>
+      <c r="J83" s="1">
+        <f t="shared" ref="J83:J89" si="11">ABS(G$3-I83)</f>
+        <v>0.20792079207920788</v>
+      </c>
+      <c r="K83" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.20792079207920788</v>
+      </c>
+      <c r="M83" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N83" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O83" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P83" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q83" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R83" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S83" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B84" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C84" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E84" s="1">
+        <v>700</v>
+      </c>
+      <c r="F84" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G84" s="1">
+        <v>101</v>
+      </c>
+      <c r="H84" s="1">
+        <v>90</v>
+      </c>
+      <c r="I84" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.8910891089108911</v>
+      </c>
+      <c r="J84" s="1">
+        <f t="shared" si="11"/>
+        <v>0.1089108910891089</v>
+      </c>
+      <c r="K84" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.1089108910891089</v>
+      </c>
+      <c r="M84" s="4">
+        <v>46272</v>
+      </c>
+      <c r="N84" s="1">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>37</v>
+      </c>
+      <c r="O84" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P84" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q84" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R84" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="S84" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B85" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C85" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E85" s="1">
+        <v>800</v>
+      </c>
+      <c r="F85" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G85" s="1">
+        <v>101</v>
+      </c>
+      <c r="H85" s="1">
+        <v>3</v>
+      </c>
+      <c r="I85" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>2.9702970297029702E-2</v>
+      </c>
+      <c r="J85" s="1">
+        <f t="shared" si="11"/>
+        <v>0.97029702970297027</v>
+      </c>
+      <c r="K85" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.97029702970297027</v>
+      </c>
+      <c r="M85" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N85" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O85" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P85" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q85" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R85" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="O82" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P82" s="1">
-        <v>900</v>
-      </c>
-      <c r="Q82" s="9">
-        <v>12260416</v>
-      </c>
-      <c r="R82" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="S82" s="1">
+      <c r="S85" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B86" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C86" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F86" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G86" s="1">
+        <v>100</v>
+      </c>
+      <c r="H86" s="1">
+        <v>69</v>
+      </c>
+      <c r="I86" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.69</v>
+      </c>
+      <c r="J86" s="1">
+        <f t="shared" si="11"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="K86" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="M86" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N86" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O86" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P86" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q86" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R86" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="S86" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B83" s="4"/>
-      <c r="I83" s="3"/>
-      <c r="J83" s="1"/>
-      <c r="K83" s="5"/>
-      <c r="M83" s="4">
-        <v>46265</v>
-      </c>
-      <c r="N83" s="12">
-        <f>WEEKNUM(Tabla2610[[#This Row],[Fecha]])</f>
-        <v>36</v>
-      </c>
-      <c r="O83" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P83" s="1" t="s">
+    <row r="87" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B87" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C87" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F87" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G87" s="1">
+        <v>86</v>
+      </c>
+      <c r="H87" s="1">
+        <v>14</v>
+      </c>
+      <c r="I87" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.16279069767441862</v>
+      </c>
+      <c r="J87" s="1">
+        <f t="shared" si="11"/>
+        <v>0.83720930232558133</v>
+      </c>
+      <c r="K87" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.83720930232558133</v>
+      </c>
+      <c r="M87" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N87" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O87" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P87" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q87" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R87" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="S87" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B88" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C88" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F88" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G88" s="1">
+        <v>83</v>
+      </c>
+      <c r="H88" s="1">
+        <v>17</v>
+      </c>
+      <c r="I88" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.20481927710843373</v>
+      </c>
+      <c r="J88" s="1">
+        <f>ABS(G$3-I88)</f>
+        <v>0.79518072289156627</v>
+      </c>
+      <c r="K88" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.79518072289156627</v>
+      </c>
+      <c r="M88" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N88" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O88" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P88" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q88" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R88" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S88" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B89" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C89" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F89" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G89" s="1">
+        <v>45</v>
+      </c>
+      <c r="H89" s="1">
+        <v>7</v>
+      </c>
+      <c r="I89" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.15555555555555556</v>
+      </c>
+      <c r="J89" s="1">
+        <f t="shared" si="11"/>
+        <v>0.84444444444444444</v>
+      </c>
+      <c r="K89" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.84444444444444444</v>
+      </c>
+      <c r="M89" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N89" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P89" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q89" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R89" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="Q83" s="9">
-        <v>12260415</v>
-      </c>
-      <c r="R83" s="1" t="s">
+      <c r="S89" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B90" s="4">
+        <v>46272</v>
+      </c>
+      <c r="C90" s="1">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>37</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F90" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G90" s="1">
+        <v>33</v>
+      </c>
+      <c r="H90" s="1">
+        <v>7</v>
+      </c>
+      <c r="I90" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.21212121212121213</v>
+      </c>
+      <c r="J90" s="1">
+        <f>ABS(G$3-I90)</f>
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="K90" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="M90" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N90" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O90" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P90" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q90" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R90" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="S90" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B91" s="4">
+        <v>46282</v>
+      </c>
+      <c r="C91" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>38</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E91" s="1">
+        <v>100</v>
+      </c>
+      <c r="F91" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G91" s="1">
+        <v>122</v>
+      </c>
+      <c r="H91" s="1">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>4.0983606557377046E-2</v>
+      </c>
+      <c r="J91" s="14">
+        <f t="shared" ref="J91:J97" si="12">ABS(G$3-I91)</f>
+        <v>0.95901639344262291</v>
+      </c>
+      <c r="K91" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.95901639344262291</v>
+      </c>
+      <c r="M91" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N91" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O91" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P91" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q91" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R91" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="S83" s="1">
+      <c r="S91" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B84" s="4"/>
-      <c r="I84" s="3"/>
-      <c r="J84" s="1"/>
-      <c r="K84" s="5"/>
-      <c r="M84" s="4"/>
-    </row>
-    <row r="85" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B85" s="4"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="1"/>
-      <c r="K85" s="5"/>
-      <c r="M85" s="4"/>
-    </row>
-    <row r="86" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B86" s="4"/>
-      <c r="I86" s="3"/>
-      <c r="J86" s="1"/>
-      <c r="K86" s="5"/>
-      <c r="M86" s="4"/>
-    </row>
-    <row r="87" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B87" s="4"/>
-      <c r="I87" s="3"/>
-      <c r="J87" s="1"/>
-      <c r="K87" s="5"/>
-      <c r="M87" s="4"/>
-    </row>
-    <row r="88" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B88" s="4"/>
-      <c r="I88" s="3"/>
-      <c r="J88" s="1"/>
-      <c r="K88" s="5"/>
-      <c r="M88" s="4"/>
-    </row>
-    <row r="89" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B89" s="4"/>
-      <c r="I89" s="3"/>
-      <c r="J89" s="1"/>
-      <c r="K89" s="5"/>
-      <c r="M89" s="4"/>
-    </row>
-    <row r="90" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B90" s="4"/>
-      <c r="I90" s="3"/>
-      <c r="J90" s="1"/>
-      <c r="K90" s="5"/>
-      <c r="M90" s="4"/>
-    </row>
-    <row r="91" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B91" s="4"/>
-      <c r="I91" s="3"/>
-      <c r="J91" s="1"/>
-      <c r="K91" s="5"/>
-      <c r="M91" s="4"/>
-    </row>
     <row r="92" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B92" s="4"/>
-      <c r="I92" s="3"/>
-      <c r="J92" s="1"/>
-      <c r="K92" s="5"/>
-      <c r="M92" s="4"/>
+      <c r="B92" s="4">
+        <v>46282</v>
+      </c>
+      <c r="C92" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>38</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E92" s="1">
+        <v>200</v>
+      </c>
+      <c r="F92" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G92" s="1">
+        <v>120</v>
+      </c>
+      <c r="H92" s="1">
+        <v>7</v>
+      </c>
+      <c r="I92" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>5.8333333333333334E-2</v>
+      </c>
+      <c r="J92" s="14">
+        <f t="shared" si="12"/>
+        <v>0.94166666666666665</v>
+      </c>
+      <c r="K92" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.94166666666666665</v>
+      </c>
+      <c r="M92" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N92" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O92" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P92" s="1">
+        <v>600</v>
+      </c>
+      <c r="Q92" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R92" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="S92" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="93" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B93" s="4"/>
-      <c r="I93" s="3"/>
-      <c r="J93" s="1"/>
-      <c r="K93" s="5"/>
-      <c r="M93" s="4"/>
+      <c r="B93" s="4">
+        <v>46282</v>
+      </c>
+      <c r="C93" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>38</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E93" s="1">
+        <v>300</v>
+      </c>
+      <c r="F93" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G93" s="1">
+        <v>100</v>
+      </c>
+      <c r="H93" s="1">
+        <v>3</v>
+      </c>
+      <c r="I93" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0.03</v>
+      </c>
+      <c r="J93" s="14">
+        <f t="shared" si="12"/>
+        <v>0.97</v>
+      </c>
+      <c r="K93" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.97</v>
+      </c>
+      <c r="M93" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N93" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O93" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P93" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q93" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R93" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S93" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="94" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B94" s="4"/>
-      <c r="I94" s="3"/>
-      <c r="J94" s="1"/>
-      <c r="K94" s="5"/>
-      <c r="M94" s="4"/>
+      <c r="B94" s="4">
+        <v>46282</v>
+      </c>
+      <c r="C94" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>38</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E94" s="1">
+        <v>400</v>
+      </c>
+      <c r="F94" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G94" s="1">
+        <v>119</v>
+      </c>
+      <c r="H94" s="1">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>3.3613445378151259E-2</v>
+      </c>
+      <c r="J94" s="14">
+        <f t="shared" si="12"/>
+        <v>0.96638655462184875</v>
+      </c>
+      <c r="K94" s="12">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.96638655462184875</v>
+      </c>
+      <c r="M94" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N94" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P94" s="1">
+        <v>800</v>
+      </c>
+      <c r="Q94" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R94" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="S94" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="95" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B95" s="4"/>
-      <c r="I95" s="3"/>
-      <c r="J95" s="1"/>
-      <c r="K95" s="5"/>
-      <c r="M95" s="4"/>
+      <c r="B95" s="4">
+        <v>46282</v>
+      </c>
+      <c r="C95" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>38</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E95" s="1">
+        <v>500</v>
+      </c>
+      <c r="F95" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G95" s="1">
+        <v>124</v>
+      </c>
+      <c r="H95" s="1">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>0</v>
+      </c>
+      <c r="J95" s="14">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="K95" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>1</v>
+      </c>
+      <c r="M95" s="4">
+        <v>46282</v>
+      </c>
+      <c r="N95" s="14">
+        <f>WEEKNUM(Tabla2610[[#This Row],[07/09/2026]])</f>
+        <v>38</v>
+      </c>
+      <c r="O95" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P95" s="1">
+        <v>800</v>
+      </c>
+      <c r="Q95" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="R95" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="S95" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="96" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B96" s="4"/>
-      <c r="I96" s="3"/>
-      <c r="J96" s="1"/>
-      <c r="K96" s="5"/>
+      <c r="B96" s="4">
+        <v>46282</v>
+      </c>
+      <c r="C96" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>38</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E96" s="1">
+        <v>600</v>
+      </c>
+      <c r="F96" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G96" s="1">
+        <v>119</v>
+      </c>
+      <c r="H96" s="1">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>4.2016806722689079E-2</v>
+      </c>
+      <c r="J96" s="14">
+        <f t="shared" si="12"/>
+        <v>0.95798319327731096</v>
+      </c>
+      <c r="K96" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.95798319327731096</v>
+      </c>
       <c r="M96" s="4"/>
+      <c r="N96" s="14"/>
+      <c r="Q96" s="9"/>
     </row>
     <row r="97" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B97" s="4"/>
-      <c r="I97" s="3"/>
-      <c r="J97" s="1"/>
-      <c r="K97" s="5"/>
+      <c r="B97" s="4">
+        <v>46282</v>
+      </c>
+      <c r="C97" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>38</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E97" s="1">
+        <v>700</v>
+      </c>
+      <c r="F97" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G97" s="1">
+        <v>118</v>
+      </c>
+      <c r="H97" s="1">
+        <v>2</v>
+      </c>
+      <c r="I97" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="J97" s="14">
+        <f t="shared" si="12"/>
+        <v>0.98305084745762716</v>
+      </c>
+      <c r="K97" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.98305084745762716</v>
+      </c>
       <c r="M97" s="4"/>
     </row>
     <row r="98" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B98" s="4"/>
-      <c r="I98" s="3"/>
-      <c r="J98" s="1"/>
-      <c r="K98" s="5"/>
+      <c r="B98" s="4">
+        <v>46282</v>
+      </c>
+      <c r="C98" s="14">
+        <f>WEEKNUM(Tabla158[[#This Row],[Fecha]])</f>
+        <v>38</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E98" s="1">
+        <v>800</v>
+      </c>
+      <c r="F98" s="9">
+        <v>12289507</v>
+      </c>
+      <c r="G98" s="1">
+        <v>112</v>
+      </c>
+      <c r="H98" s="1">
+        <v>4</v>
+      </c>
+      <c r="I98" s="3">
+        <f>Tabla158[[#This Row],[Piezas NOK]]/Tabla158[[#This Row],[Piezas OK]]</f>
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="J98" s="14">
+        <f>ABS(G$3-I98)</f>
+        <v>0.9642857142857143</v>
+      </c>
+      <c r="K98" s="5">
+        <f>Tabla158[[#This Row],[FTQ]]</f>
+        <v>0.9642857142857143</v>
+      </c>
       <c r="M98" s="4"/>
     </row>
     <row r="99" spans="2:13" x14ac:dyDescent="0.3">
@@ -30268,6 +31069,8 @@
       <c r="J215" s="1"/>
       <c r="K215" s="5"/>
       <c r="M215" s="4"/>
+      <c r="U215" s="1"/>
+      <c r="V215" s="1"/>
     </row>
     <row r="216" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B216" s="4"/>
@@ -30275,6 +31078,8 @@
       <c r="J216" s="1"/>
       <c r="K216" s="5"/>
       <c r="M216" s="4"/>
+      <c r="U216" s="1"/>
+      <c r="V216" s="1"/>
     </row>
     <row r="217" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B217" s="4"/>
@@ -30310,8 +31115,6 @@
       <c r="J221" s="1"/>
       <c r="K221" s="5"/>
       <c r="M221" s="4"/>
-      <c r="U221" s="1"/>
-      <c r="V221" s="1"/>
     </row>
     <row r="222" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B222" s="4"/>
@@ -30319,8 +31122,6 @@
       <c r="J222" s="1"/>
       <c r="K222" s="5"/>
       <c r="M222" s="4"/>
-      <c r="U222" s="1"/>
-      <c r="V222" s="1"/>
     </row>
     <row r="223" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B223" s="4"/>
@@ -30390,21 +31191,21 @@
       <c r="I232" s="3"/>
       <c r="J232" s="1"/>
       <c r="K232" s="5"/>
-      <c r="M232" s="4"/>
+      <c r="M232" s="8"/>
     </row>
     <row r="233" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B233" s="4"/>
       <c r="I233" s="3"/>
       <c r="J233" s="1"/>
       <c r="K233" s="5"/>
-      <c r="M233" s="4"/>
+      <c r="M233" s="8"/>
     </row>
     <row r="234" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B234" s="4"/>
       <c r="I234" s="3"/>
       <c r="J234" s="1"/>
       <c r="K234" s="5"/>
-      <c r="M234" s="4"/>
+      <c r="M234" s="8"/>
     </row>
     <row r="235" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B235" s="4"/>
@@ -30432,21 +31233,21 @@
       <c r="I238" s="3"/>
       <c r="J238" s="1"/>
       <c r="K238" s="5"/>
-      <c r="M238" s="8"/>
+      <c r="M238" s="4"/>
     </row>
     <row r="239" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B239" s="4"/>
       <c r="I239" s="3"/>
       <c r="J239" s="1"/>
       <c r="K239" s="5"/>
-      <c r="M239" s="8"/>
+      <c r="M239" s="4"/>
     </row>
     <row r="240" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B240" s="4"/>
       <c r="I240" s="3"/>
       <c r="J240" s="1"/>
       <c r="K240" s="5"/>
-      <c r="M240" s="8"/>
+      <c r="M240" s="4"/>
     </row>
     <row r="241" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B241" s="4"/>
@@ -30697,67 +31498,55 @@
       <c r="B276" s="4"/>
       <c r="I276" s="3"/>
       <c r="J276" s="1"/>
-      <c r="K276" s="5"/>
       <c r="M276" s="4"/>
     </row>
     <row r="277" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B277" s="4"/>
       <c r="I277" s="3"/>
       <c r="J277" s="1"/>
-      <c r="K277" s="5"/>
       <c r="M277" s="4"/>
     </row>
     <row r="278" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B278" s="4"/>
       <c r="I278" s="3"/>
       <c r="J278" s="1"/>
-      <c r="K278" s="5"/>
       <c r="M278" s="4"/>
     </row>
     <row r="279" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B279" s="4"/>
       <c r="I279" s="3"/>
       <c r="J279" s="1"/>
-      <c r="K279" s="5"/>
       <c r="M279" s="4"/>
     </row>
     <row r="280" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B280" s="4"/>
       <c r="I280" s="3"/>
       <c r="J280" s="1"/>
-      <c r="K280" s="5"/>
-      <c r="M280" s="4"/>
     </row>
     <row r="281" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B281" s="4"/>
       <c r="I281" s="3"/>
       <c r="J281" s="1"/>
-      <c r="K281" s="5"/>
-      <c r="M281" s="4"/>
     </row>
     <row r="282" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B282" s="4"/>
       <c r="I282" s="3"/>
       <c r="J282" s="1"/>
-      <c r="M282" s="4"/>
     </row>
     <row r="283" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B283" s="4"/>
       <c r="I283" s="3"/>
       <c r="J283" s="1"/>
-      <c r="M283" s="4"/>
     </row>
     <row r="284" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B284" s="4"/>
       <c r="I284" s="3"/>
       <c r="J284" s="1"/>
-      <c r="M284" s="4"/>
     </row>
     <row r="285" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B285" s="4"/>
       <c r="I285" s="3"/>
       <c r="J285" s="1"/>
-      <c r="M285" s="4"/>
     </row>
     <row r="286" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B286" s="4"/>
@@ -30820,6 +31609,9 @@
       <c r="J297" s="1"/>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>0</v>
+      </c>
       <c r="B298" s="4"/>
       <c r="I298" s="3"/>
       <c r="J298" s="1"/>
@@ -30850,9 +31642,6 @@
       <c r="J303" s="1"/>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A304" t="s">
-        <v>0</v>
-      </c>
       <c r="B304" s="4"/>
       <c r="I304" s="3"/>
       <c r="J304" s="1"/>
@@ -31023,6 +31812,9 @@
       <c r="J337" s="1"/>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>0</v>
+      </c>
       <c r="B338" s="4"/>
       <c r="I338" s="3"/>
       <c r="J338" s="1"/>
@@ -31053,9 +31845,6 @@
       <c r="J343" s="1"/>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A344" t="s">
-        <v>0</v>
-      </c>
       <c r="B344" s="4"/>
       <c r="I344" s="3"/>
       <c r="J344" s="1"/>
@@ -31449,31 +32238,49 @@
       <c r="B422" s="4"/>
       <c r="I422" s="3"/>
       <c r="J422" s="1"/>
+      <c r="M422" s="7"/>
+      <c r="N422" s="7"/>
+      <c r="O422" s="7"/>
     </row>
     <row r="423" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B423" s="4"/>
       <c r="I423" s="3"/>
       <c r="J423" s="1"/>
+      <c r="M423" s="7"/>
+      <c r="N423" s="7"/>
+      <c r="O423" s="7"/>
     </row>
     <row r="424" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B424" s="4"/>
       <c r="I424" s="3"/>
       <c r="J424" s="1"/>
+      <c r="M424" s="7"/>
+      <c r="N424" s="7"/>
+      <c r="O424" s="7"/>
     </row>
     <row r="425" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B425" s="4"/>
       <c r="I425" s="3"/>
       <c r="J425" s="1"/>
+      <c r="M425" s="7"/>
+      <c r="N425" s="7"/>
+      <c r="O425" s="7"/>
     </row>
     <row r="426" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B426" s="4"/>
       <c r="I426" s="3"/>
       <c r="J426" s="1"/>
+      <c r="M426" s="7"/>
+      <c r="N426" s="7"/>
+      <c r="O426" s="7"/>
     </row>
     <row r="427" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B427" s="4"/>
       <c r="I427" s="3"/>
       <c r="J427" s="1"/>
+      <c r="M427" s="7"/>
+      <c r="N427" s="7"/>
+      <c r="O427" s="7"/>
     </row>
     <row r="428" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B428" s="4"/>
@@ -31584,7 +32391,7 @@
       <c r="I441" s="3"/>
       <c r="J441" s="1"/>
       <c r="M441" s="7"/>
-      <c r="N441" s="7"/>
+      <c r="N441" s="8"/>
       <c r="O441" s="7"/>
     </row>
     <row r="442" spans="2:15" x14ac:dyDescent="0.3">
@@ -31632,7 +32439,7 @@
       <c r="I447" s="3"/>
       <c r="J447" s="1"/>
       <c r="M447" s="7"/>
-      <c r="N447" s="8"/>
+      <c r="N447" s="7"/>
       <c r="O447" s="7"/>
     </row>
     <row r="448" spans="2:15" x14ac:dyDescent="0.3">
@@ -31815,49 +32622,31 @@
       <c r="B470" s="4"/>
       <c r="I470" s="3"/>
       <c r="J470" s="1"/>
-      <c r="M470" s="7"/>
-      <c r="N470" s="7"/>
-      <c r="O470" s="7"/>
     </row>
     <row r="471" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B471" s="4"/>
       <c r="I471" s="3"/>
       <c r="J471" s="1"/>
-      <c r="M471" s="7"/>
-      <c r="N471" s="7"/>
-      <c r="O471" s="7"/>
     </row>
     <row r="472" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B472" s="4"/>
       <c r="I472" s="3"/>
       <c r="J472" s="1"/>
-      <c r="M472" s="7"/>
-      <c r="N472" s="7"/>
-      <c r="O472" s="7"/>
     </row>
     <row r="473" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B473" s="4"/>
       <c r="I473" s="3"/>
       <c r="J473" s="1"/>
-      <c r="M473" s="7"/>
-      <c r="N473" s="7"/>
-      <c r="O473" s="7"/>
     </row>
     <row r="474" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B474" s="4"/>
       <c r="I474" s="3"/>
       <c r="J474" s="1"/>
-      <c r="M474" s="7"/>
-      <c r="N474" s="7"/>
-      <c r="O474" s="7"/>
     </row>
     <row r="475" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B475" s="4"/>
       <c r="I475" s="3"/>
       <c r="J475" s="1"/>
-      <c r="M475" s="7"/>
-      <c r="N475" s="7"/>
-      <c r="O475" s="7"/>
     </row>
     <row r="476" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B476" s="4"/>
@@ -32865,6 +33654,9 @@
       <c r="J676" s="1"/>
     </row>
     <row r="677" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A677" t="s">
+        <v>0</v>
+      </c>
       <c r="B677" s="4"/>
       <c r="I677" s="3"/>
       <c r="J677" s="1"/>
@@ -33060,9 +33852,6 @@
       <c r="J712" s="1"/>
     </row>
     <row r="713" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A713" t="s">
-        <v>0</v>
-      </c>
       <c r="B713" s="4"/>
       <c r="I713" s="3"/>
       <c r="J713" s="1"/>
@@ -33102,90 +33891,90 @@
       <c r="I720" s="3"/>
       <c r="J720" s="1"/>
     </row>
-    <row r="721" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B721" s="4"/>
       <c r="I721" s="3"/>
       <c r="J721" s="1"/>
     </row>
-    <row r="722" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B722" s="4"/>
       <c r="I722" s="3"/>
       <c r="J722" s="1"/>
     </row>
-    <row r="723" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B723" s="4"/>
       <c r="I723" s="3"/>
       <c r="J723" s="1"/>
     </row>
-    <row r="724" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B724" s="4"/>
       <c r="I724" s="3"/>
       <c r="J724" s="1"/>
     </row>
-    <row r="725" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B725" s="4"/>
       <c r="I725" s="3"/>
       <c r="J725" s="1"/>
     </row>
-    <row r="726" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B726" s="4"/>
       <c r="I726" s="3"/>
       <c r="J726" s="1"/>
     </row>
-    <row r="727" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B727" s="4"/>
       <c r="I727" s="3"/>
       <c r="J727" s="1"/>
     </row>
-    <row r="728" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B728" s="4"/>
       <c r="I728" s="3"/>
       <c r="J728" s="1"/>
     </row>
-    <row r="729" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B729" s="4"/>
       <c r="I729" s="3"/>
       <c r="J729" s="1"/>
     </row>
-    <row r="730" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B730" s="4"/>
       <c r="I730" s="3"/>
       <c r="J730" s="1"/>
     </row>
-    <row r="731" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A731" t="s">
+        <v>0</v>
+      </c>
       <c r="B731" s="4"/>
       <c r="I731" s="3"/>
       <c r="J731" s="1"/>
     </row>
-    <row r="732" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B732" s="4"/>
       <c r="I732" s="3"/>
       <c r="J732" s="1"/>
     </row>
-    <row r="733" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B733" s="4"/>
       <c r="I733" s="3"/>
       <c r="J733" s="1"/>
     </row>
-    <row r="734" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B734" s="4"/>
       <c r="I734" s="3"/>
       <c r="J734" s="1"/>
     </row>
-    <row r="735" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B735" s="4"/>
       <c r="I735" s="3"/>
       <c r="J735" s="1"/>
     </row>
-    <row r="736" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B736" s="4"/>
       <c r="I736" s="3"/>
       <c r="J736" s="1"/>
     </row>
     <row r="737" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A737" t="s">
-        <v>0</v>
-      </c>
       <c r="B737" s="4"/>
       <c r="I737" s="3"/>
       <c r="J737" s="1"/>
@@ -33246,6 +34035,9 @@
       <c r="J748" s="1"/>
     </row>
     <row r="749" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A749" t="s">
+        <v>0</v>
+      </c>
       <c r="B749" s="4"/>
       <c r="I749" s="3"/>
       <c r="J749" s="1"/>
@@ -33265,85 +34057,82 @@
       <c r="I752" s="3"/>
       <c r="J752" s="1"/>
     </row>
-    <row r="753" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="753" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B753" s="4"/>
       <c r="I753" s="3"/>
       <c r="J753" s="1"/>
     </row>
-    <row r="754" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="754" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B754" s="4"/>
       <c r="I754" s="3"/>
       <c r="J754" s="1"/>
     </row>
-    <row r="755" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A755" t="s">
-        <v>0</v>
-      </c>
+    <row r="755" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B755" s="4"/>
       <c r="I755" s="3"/>
       <c r="J755" s="1"/>
     </row>
-    <row r="756" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="756" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B756" s="4"/>
       <c r="I756" s="3"/>
       <c r="J756" s="1"/>
     </row>
-    <row r="757" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="757" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B757" s="4"/>
       <c r="I757" s="3"/>
       <c r="J757" s="1"/>
     </row>
-    <row r="758" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="758" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B758" s="4"/>
       <c r="I758" s="3"/>
       <c r="J758" s="1"/>
     </row>
-    <row r="759" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="759" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B759" s="4"/>
       <c r="I759" s="3"/>
       <c r="J759" s="1"/>
     </row>
-    <row r="760" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="760" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B760" s="4"/>
       <c r="I760" s="3"/>
       <c r="J760" s="1"/>
     </row>
-    <row r="761" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="761" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B761" s="4"/>
       <c r="I761" s="3"/>
       <c r="J761" s="1"/>
     </row>
-    <row r="762" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="762" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B762" s="4"/>
       <c r="I762" s="3"/>
       <c r="J762" s="1"/>
     </row>
-    <row r="763" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="763" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B763" s="4"/>
       <c r="I763" s="3"/>
       <c r="J763" s="1"/>
     </row>
-    <row r="764" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="764" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B764" s="4"/>
       <c r="I764" s="3"/>
       <c r="J764" s="1"/>
     </row>
-    <row r="765" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="765" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B765" s="4"/>
       <c r="I765" s="3"/>
       <c r="J765" s="1"/>
     </row>
-    <row r="766" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="766" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B766" s="4"/>
       <c r="I766" s="3"/>
       <c r="J766" s="1"/>
     </row>
-    <row r="767" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="767" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B767" s="4"/>
       <c r="I767" s="3"/>
       <c r="J767" s="1"/>
     </row>
-    <row r="768" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="768" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B768" s="4"/>
       <c r="I768" s="3"/>
       <c r="J768" s="1"/>
@@ -33429,7 +34218,6 @@
       <c r="J784" s="1"/>
     </row>
     <row r="785" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B785" s="4"/>
       <c r="I785" s="3"/>
       <c r="J785" s="1"/>
     </row>
@@ -33459,6 +34247,7 @@
       <c r="J790" s="1"/>
     </row>
     <row r="791" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B791" s="4"/>
       <c r="I791" s="3"/>
       <c r="J791" s="1"/>
     </row>
@@ -33489,6 +34278,7 @@
     </row>
     <row r="797" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B797" s="4"/>
+      <c r="G797" s="4"/>
       <c r="I797" s="3"/>
       <c r="J797" s="1"/>
     </row>
@@ -33519,7 +34309,6 @@
     </row>
     <row r="803" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B803" s="4"/>
-      <c r="G803" s="4"/>
       <c r="I803" s="3"/>
       <c r="J803" s="1"/>
     </row>
@@ -33627,36 +34416,6 @@
       <c r="B824" s="4"/>
       <c r="I824" s="3"/>
       <c r="J824" s="1"/>
-    </row>
-    <row r="825" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B825" s="4"/>
-      <c r="I825" s="3"/>
-      <c r="J825" s="1"/>
-    </row>
-    <row r="826" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B826" s="4"/>
-      <c r="I826" s="3"/>
-      <c r="J826" s="1"/>
-    </row>
-    <row r="827" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B827" s="4"/>
-      <c r="I827" s="3"/>
-      <c r="J827" s="1"/>
-    </row>
-    <row r="828" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B828" s="4"/>
-      <c r="I828" s="3"/>
-      <c r="J828" s="1"/>
-    </row>
-    <row r="829" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B829" s="4"/>
-      <c r="I829" s="3"/>
-      <c r="J829" s="1"/>
-    </row>
-    <row r="830" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B830" s="4"/>
-      <c r="I830" s="3"/>
-      <c r="J830" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
